--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N35_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.11200288085544</v>
+        <v>9.76820046813901</v>
       </c>
       <c r="D2" t="n">
-        <v>59.85671061023662</v>
+        <v>9.72671547416345</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
